--- a/static/data/exports/Retro_AS_GE_2024.xlsx
+++ b/static/data/exports/Retro_AS_GE_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_AS_GE_2024.xlsx
+++ b/static/data/exports/Retro_AS_GE_2024.xlsx
@@ -5305,20 +5305,20 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1717777</v>
+        <v>1717778</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Surat Zaman Mondal</t>
+          <t>Tahidur Rahman</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SUCI</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>19871</v>
+        <v>19862</v>
       </c>
       <c r="E79" t="n">
         <v>161</v>
@@ -5342,12 +5342,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Surat Zaman Mondal</t>
+          <t>Tahidur Rahman</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>SUCI</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="Q79" t="b">
@@ -5367,20 +5367,20 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1717778</v>
+        <v>1717777</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tahidur Rahman</t>
+          <t>Surat Zaman Mondal</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>SUCI</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>19862</v>
+        <v>19871</v>
       </c>
       <c r="E80" t="n">
         <v>161</v>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Tahidur Rahman</t>
+          <t>Surat Zaman Mondal</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>SUCI</t>
         </is>
       </c>
       <c r="Q80" t="b">
@@ -42381,11 +42381,11 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>1718376</v>
+        <v>1718375</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Sikha Sarma</t>
+          <t>Samsul Alam</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -42418,7 +42418,7 @@
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>Sikha Sarma</t>
+          <t>Samsul Alam</t>
         </is>
       </c>
       <c r="L677" t="inlineStr">
@@ -42443,11 +42443,11 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>1718375</v>
+        <v>1718376</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Samsul Alam</t>
+          <t>Sikha Sarma</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -42480,7 +42480,7 @@
       </c>
       <c r="K678" t="inlineStr">
         <is>
-          <t>Samsul Alam</t>
+          <t>Sikha Sarma</t>
         </is>
       </c>
       <c r="L678" t="inlineStr">
@@ -45233,26 +45233,26 @@
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>1718422</v>
+        <v>1718421</v>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Abdul Hoque</t>
+          <t>Sailen Ch Malakar</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BGanP</t>
         </is>
       </c>
       <c r="D723" t="n">
-        <v>19861</v>
+        <v>19867</v>
       </c>
       <c r="E723" t="n">
         <v>362</v>
       </c>
       <c r="F723" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="G723" t="n">
         <v>9</v>
@@ -45270,12 +45270,12 @@
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>Abdul Hoque</t>
+          <t>Sailen Ch Malakar</t>
         </is>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BGanP</t>
         </is>
       </c>
       <c r="Q723" t="b">
@@ -45295,26 +45295,26 @@
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>1718421</v>
+        <v>1718422</v>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Sailen Ch Malakar</t>
+          <t>Abdul Hoque</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>BGanP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D724" t="n">
-        <v>19867</v>
+        <v>19861</v>
       </c>
       <c r="E724" t="n">
         <v>362</v>
       </c>
       <c r="F724" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G724" t="n">
         <v>9</v>
@@ -45332,12 +45332,12 @@
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>Sailen Ch Malakar</t>
+          <t>Abdul Hoque</t>
         </is>
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>BGanP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q724" t="b">
@@ -50689,20 +50689,20 @@
     </row>
     <row r="811">
       <c r="A811" t="n">
-        <v>1718510</v>
+        <v>1718509</v>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Abdul Hoque</t>
+          <t>Anima Deka Gupta</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="D811" t="n">
-        <v>19861</v>
+        <v>19862</v>
       </c>
       <c r="E811" t="n">
         <v>872</v>
@@ -50726,12 +50726,12 @@
       </c>
       <c r="K811" t="inlineStr">
         <is>
-          <t>Abdul Hoque</t>
+          <t>Anima Deka Gupta</t>
         </is>
       </c>
       <c r="L811" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>VPI</t>
         </is>
       </c>
       <c r="Q811" t="b">
@@ -50751,20 +50751,20 @@
     </row>
     <row r="812">
       <c r="A812" t="n">
-        <v>1718509</v>
+        <v>1718510</v>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Anima Deka Gupta</t>
+          <t>Abdul Hoque</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D812" t="n">
-        <v>19862</v>
+        <v>19861</v>
       </c>
       <c r="E812" t="n">
         <v>872</v>
@@ -50788,12 +50788,12 @@
       </c>
       <c r="K812" t="inlineStr">
         <is>
-          <t>Anima Deka Gupta</t>
+          <t>Abdul Hoque</t>
         </is>
       </c>
       <c r="L812" t="inlineStr">
         <is>
-          <t>VPI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q812" t="b">
@@ -83983,11 +83983,11 @@
     </row>
     <row r="1348">
       <c r="A1348" t="n">
-        <v>1719047</v>
+        <v>1719046</v>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Muzakkir Hasan Laskar</t>
+          <t>Gopal Chandra Paul</t>
         </is>
       </c>
       <c r="C1348" t="inlineStr">
@@ -84020,7 +84020,7 @@
       </c>
       <c r="K1348" t="inlineStr">
         <is>
-          <t>Muzakkir Hasan Laskar</t>
+          <t>Gopal Chandra Paul</t>
         </is>
       </c>
       <c r="L1348" t="inlineStr">
@@ -84045,11 +84045,11 @@
     </row>
     <row r="1349">
       <c r="A1349" t="n">
-        <v>1719046</v>
+        <v>1719047</v>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Gopal Chandra Paul</t>
+          <t>Muzakkir Hasan Laskar</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr">
@@ -84082,7 +84082,7 @@
       </c>
       <c r="K1349" t="inlineStr">
         <is>
-          <t>Gopal Chandra Paul</t>
+          <t>Muzakkir Hasan Laskar</t>
         </is>
       </c>
       <c r="L1349" t="inlineStr">
